--- a/school_lublino/ceilling/vor_lublino_ceiling.xlsx
+++ b/school_lublino/ceilling/vor_lublino_ceiling.xlsx
@@ -18,23 +18,25 @@
     <sheet name="1этВор" sheetId="10" state="hidden" r:id="rId4"/>
     <sheet name="1эт спец" sheetId="11" state="hidden" r:id="rId5"/>
     <sheet name="Вор2Вып" sheetId="12" state="hidden" r:id="rId6"/>
-    <sheet name="6.5П7,10 (2)" sheetId="22" r:id="rId7"/>
-    <sheet name="6.4П8" sheetId="21" r:id="rId8"/>
-    <sheet name="6.3П8" sheetId="20" r:id="rId9"/>
-    <sheet name="6.2П7,10" sheetId="19" r:id="rId10"/>
-    <sheet name="6.1П9" sheetId="18" r:id="rId11"/>
-    <sheet name="Общий" sheetId="13" r:id="rId12"/>
-    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId13"/>
-    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId15"/>
-    <sheet name="ПокрПом" sheetId="16" r:id="rId16"/>
+    <sheet name="9.3П8" sheetId="24" r:id="rId7"/>
+    <sheet name="7.1КрсИнж" sheetId="23" r:id="rId8"/>
+    <sheet name="6.5П7,10 (2)" sheetId="22" r:id="rId9"/>
+    <sheet name="6.4П8" sheetId="21" r:id="rId10"/>
+    <sheet name="6.3П8" sheetId="20" r:id="rId11"/>
+    <sheet name="6.2П7,10" sheetId="19" r:id="rId12"/>
+    <sheet name="6.1П9" sheetId="18" r:id="rId13"/>
+    <sheet name="Общий" sheetId="13" r:id="rId14"/>
+    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId16"/>
+    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId17"/>
+    <sheet name="ПокрПом" sheetId="16" r:id="rId18"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="188">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -596,6 +598,15 @@
   </si>
   <si>
     <t>Тип П-7</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы
+СКБ / окраска потолков /</t>
+  </si>
+  <si>
+    <t>Окраска потолка/
+окраска инженерных
+коммуникации / Тип П-6</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1326,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1829,6 +1840,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1847,33 +1882,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1913,9 +1951,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2572,6 +2611,664 @@
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="206" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+    </row>
+    <row r="2" spans="1:11" s="185" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="209"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="186">
+        <v>1</v>
+      </c>
+      <c r="B3" s="207" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="210"/>
+      <c r="K3" s="184">
+        <f>C9</f>
+        <v>155.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="203"/>
+      <c r="B4" s="203"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="203"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="204"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="180">
+        <v>102.83</v>
+      </c>
+      <c r="D6" s="204"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="183">
+        <v>21.8</v>
+      </c>
+      <c r="D7" s="204"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="178" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="180">
+        <v>30.72</v>
+      </c>
+      <c r="D8" s="204"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="182"/>
+      <c r="B9" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="183">
+        <f>SUM(C6:C8)</f>
+        <v>155.35</v>
+      </c>
+      <c r="D9" s="204"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
+      <c r="I9" s="205"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:K9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="206" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+    </row>
+    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="209"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="172">
+        <v>1</v>
+      </c>
+      <c r="B3" s="207" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="210"/>
+      <c r="K3" s="184">
+        <f>C13+G15+K16</f>
+        <v>1966.37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="208" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="205"/>
+      <c r="E5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="212"/>
+      <c r="I5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="K5" s="177" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="180">
+        <v>114.21</v>
+      </c>
+      <c r="D6" s="205"/>
+      <c r="E6" s="178">
+        <v>1</v>
+      </c>
+      <c r="F6" s="178" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="180">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="H6" s="212"/>
+      <c r="I6" s="178">
+        <v>1</v>
+      </c>
+      <c r="J6" s="178" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" s="180">
+        <v>127.87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="183">
+        <v>68.75</v>
+      </c>
+      <c r="D7" s="205"/>
+      <c r="E7" s="181">
+        <v>2</v>
+      </c>
+      <c r="F7" s="181" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="183">
+        <v>72.16</v>
+      </c>
+      <c r="H7" s="212"/>
+      <c r="I7" s="181">
+        <v>2</v>
+      </c>
+      <c r="J7" s="181" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" s="183">
+        <v>73.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="178" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="180">
+        <v>68.81</v>
+      </c>
+      <c r="D8" s="205"/>
+      <c r="E8" s="178">
+        <v>3</v>
+      </c>
+      <c r="F8" s="178" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="180">
+        <v>68.27</v>
+      </c>
+      <c r="H8" s="212"/>
+      <c r="I8" s="178">
+        <v>3</v>
+      </c>
+      <c r="J8" s="178" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="180">
+        <v>71.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="181" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="183">
+        <v>69.069999999999993</v>
+      </c>
+      <c r="D9" s="205"/>
+      <c r="E9" s="181">
+        <v>4</v>
+      </c>
+      <c r="F9" s="181" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="183">
+        <v>68.3</v>
+      </c>
+      <c r="H9" s="212"/>
+      <c r="I9" s="181">
+        <v>4</v>
+      </c>
+      <c r="J9" s="181" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" s="183">
+        <v>67.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="178">
+        <v>5</v>
+      </c>
+      <c r="B10" s="178" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="180">
+        <v>68.78</v>
+      </c>
+      <c r="D10" s="205"/>
+      <c r="E10" s="178">
+        <v>5</v>
+      </c>
+      <c r="F10" s="178" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="180">
+        <v>68.64</v>
+      </c>
+      <c r="H10" s="212"/>
+      <c r="I10" s="178">
+        <v>5</v>
+      </c>
+      <c r="J10" s="178" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" s="180">
+        <v>67.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
+        <v>6</v>
+      </c>
+      <c r="B11" s="181" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="183">
+        <v>68.03</v>
+      </c>
+      <c r="D11" s="205"/>
+      <c r="E11" s="181">
+        <v>6</v>
+      </c>
+      <c r="F11" s="181" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="183">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H11" s="212"/>
+      <c r="I11" s="181">
+        <v>6</v>
+      </c>
+      <c r="J11" s="181" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" s="183">
+        <v>68.180000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="178">
+        <v>7</v>
+      </c>
+      <c r="B12" s="178" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="180">
+        <v>137.58000000000001</v>
+      </c>
+      <c r="D12" s="205"/>
+      <c r="E12" s="178">
+        <v>7</v>
+      </c>
+      <c r="F12" s="178" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="180">
+        <v>67.58</v>
+      </c>
+      <c r="H12" s="212"/>
+      <c r="I12" s="178">
+        <v>7</v>
+      </c>
+      <c r="J12" s="178" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="180">
+        <v>68.010000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="182"/>
+      <c r="B13" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="183">
+        <f>SUM(C6:C12)</f>
+        <v>595.23</v>
+      </c>
+      <c r="D13" s="205"/>
+      <c r="E13" s="181">
+        <v>8</v>
+      </c>
+      <c r="F13" s="181" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="183">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H13" s="212"/>
+      <c r="I13" s="181">
+        <v>8</v>
+      </c>
+      <c r="J13" s="181" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="183">
+        <v>67.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="211"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="178">
+        <v>9</v>
+      </c>
+      <c r="F14" s="178" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="180">
+        <v>68.27</v>
+      </c>
+      <c r="H14" s="212"/>
+      <c r="I14" s="178">
+        <v>9</v>
+      </c>
+      <c r="J14" s="178" t="s">
+        <v>179</v>
+      </c>
+      <c r="K14" s="180">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="205"/>
+      <c r="F15" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="183">
+        <f>SUM(G6:G14)</f>
+        <v>623.7399999999999</v>
+      </c>
+      <c r="H15" s="212"/>
+      <c r="I15" s="181">
+        <v>10</v>
+      </c>
+      <c r="J15" s="181" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="183">
+        <v>67.81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="J16" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="K16" s="183">
+        <f>SUM(K6:K15)</f>
+        <v>747.40000000000009</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A14:C16"/>
+    <mergeCell ref="D5:D16"/>
+    <mergeCell ref="H5:H16"/>
+    <mergeCell ref="E16:G16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
     <col min="5" max="6" width="8.77734375" customWidth="1"/>
@@ -2582,39 +3279,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="200" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="199" t="s">
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="201" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="201"/>
+      <c r="J2" s="209"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -2623,40 +3320,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="207" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="202" t="s">
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202" t="s">
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="202"/>
+      <c r="J3" s="210"/>
       <c r="K3" s="184">
         <f>C9</f>
         <v>292.98</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="195" t="s">
+      <c r="A4" s="208" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -2668,14 +3365,14 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="203"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="178">
@@ -2687,14 +3384,14 @@
       <c r="C6" s="180">
         <v>219.5</v>
       </c>
-      <c r="D6" s="203"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="196"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="181">
@@ -2706,14 +3403,14 @@
       <c r="C7" s="183">
         <v>59.48</v>
       </c>
-      <c r="D7" s="203"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="178">
@@ -2725,14 +3422,14 @@
       <c r="C8" s="180">
         <v>14</v>
       </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
-      <c r="K8" s="196"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="205"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="182" t="s">
@@ -2745,14 +3442,14 @@
         <f>SUM(C6:C8)</f>
         <v>292.98</v>
       </c>
-      <c r="D9" s="203"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="196"/>
+      <c r="D9" s="204"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
+      <c r="I9" s="205"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2771,7 +3468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2787,39 +3484,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="200" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="199" t="s">
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="201" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="201"/>
+      <c r="J2" s="209"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -2828,40 +3525,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="207" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="202" t="s">
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202" t="s">
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="202"/>
+      <c r="J3" s="210"/>
       <c r="K3" s="184">
         <f>C10+G21+K10</f>
         <v>258.09999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="195" t="s">
+      <c r="A4" s="208" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -2873,7 +3570,7 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="196"/>
+      <c r="D5" s="205"/>
       <c r="E5" s="175" t="s">
         <v>0</v>
       </c>
@@ -2883,7 +3580,7 @@
       <c r="G5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="203"/>
+      <c r="H5" s="204"/>
       <c r="I5" s="175" t="s">
         <v>0</v>
       </c>
@@ -2904,7 +3601,7 @@
       <c r="C6" s="180">
         <v>17.2</v>
       </c>
-      <c r="D6" s="196"/>
+      <c r="D6" s="205"/>
       <c r="E6" s="178">
         <v>1</v>
       </c>
@@ -2914,7 +3611,7 @@
       <c r="G6" s="180">
         <v>17.2</v>
       </c>
-      <c r="H6" s="203"/>
+      <c r="H6" s="204"/>
       <c r="I6" s="178">
         <v>1</v>
       </c>
@@ -2935,7 +3632,7 @@
       <c r="C7" s="183">
         <v>20.7</v>
       </c>
-      <c r="D7" s="196"/>
+      <c r="D7" s="205"/>
       <c r="E7" s="181">
         <v>2</v>
       </c>
@@ -2945,7 +3642,7 @@
       <c r="G7" s="183">
         <v>20.7</v>
       </c>
-      <c r="H7" s="203"/>
+      <c r="H7" s="204"/>
       <c r="I7" s="181">
         <v>2</v>
       </c>
@@ -2966,7 +3663,7 @@
       <c r="C8" s="180">
         <v>5.5</v>
       </c>
-      <c r="D8" s="196"/>
+      <c r="D8" s="205"/>
       <c r="E8" s="178">
         <v>3</v>
       </c>
@@ -2976,7 +3673,7 @@
       <c r="G8" s="180">
         <v>5.5</v>
       </c>
-      <c r="H8" s="203"/>
+      <c r="H8" s="204"/>
       <c r="I8" s="178">
         <v>3</v>
       </c>
@@ -2997,7 +3694,7 @@
       <c r="C9" s="183">
         <v>3</v>
       </c>
-      <c r="D9" s="196"/>
+      <c r="D9" s="205"/>
       <c r="E9" s="181">
         <v>4</v>
       </c>
@@ -3007,7 +3704,7 @@
       <c r="G9" s="183">
         <v>3</v>
       </c>
-      <c r="H9" s="203"/>
+      <c r="H9" s="204"/>
       <c r="I9" s="181">
         <v>4</v>
       </c>
@@ -3027,7 +3724,7 @@
         <f>SUM(C6:C9)</f>
         <v>46.4</v>
       </c>
-      <c r="D10" s="196"/>
+      <c r="D10" s="205"/>
       <c r="E10" s="178">
         <v>5</v>
       </c>
@@ -3037,7 +3734,7 @@
       <c r="G10" s="180">
         <v>6.08</v>
       </c>
-      <c r="H10" s="203"/>
+      <c r="H10" s="204"/>
       <c r="I10" s="178"/>
       <c r="J10" s="182" t="s">
         <v>93</v>
@@ -3048,10 +3745,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="198"/>
-      <c r="B11" s="198"/>
-      <c r="C11" s="198"/>
-      <c r="D11" s="196"/>
+      <c r="A11" s="211"/>
+      <c r="B11" s="211"/>
+      <c r="C11" s="211"/>
+      <c r="D11" s="205"/>
       <c r="E11" s="181">
         <v>6</v>
       </c>
@@ -3061,16 +3758,16 @@
       <c r="G11" s="183">
         <v>12.15</v>
       </c>
-      <c r="H11" s="203"/>
-      <c r="I11" s="198"/>
-      <c r="J11" s="198"/>
-      <c r="K11" s="198"/>
+      <c r="H11" s="204"/>
+      <c r="I11" s="211"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="211"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="197"/>
-      <c r="B12" s="197"/>
-      <c r="C12" s="197"/>
-      <c r="D12" s="196"/>
+      <c r="A12" s="212"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="205"/>
       <c r="E12" s="178">
         <v>7</v>
       </c>
@@ -3080,16 +3777,16 @@
       <c r="G12" s="180">
         <v>10.67</v>
       </c>
-      <c r="H12" s="203"/>
-      <c r="I12" s="197"/>
-      <c r="J12" s="197"/>
-      <c r="K12" s="197"/>
+      <c r="H12" s="204"/>
+      <c r="I12" s="212"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="212"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="197"/>
-      <c r="B13" s="197"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="196"/>
+      <c r="A13" s="212"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="205"/>
       <c r="E13" s="181">
         <v>8</v>
       </c>
@@ -3099,16 +3796,16 @@
       <c r="G13" s="183">
         <v>8.81</v>
       </c>
-      <c r="H13" s="203"/>
-      <c r="I13" s="197"/>
-      <c r="J13" s="197"/>
-      <c r="K13" s="197"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="212"/>
+      <c r="J13" s="212"/>
+      <c r="K13" s="212"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="197"/>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="196"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="205"/>
       <c r="E14" s="178">
         <v>9</v>
       </c>
@@ -3118,16 +3815,16 @@
       <c r="G14" s="180">
         <v>14.23</v>
       </c>
-      <c r="H14" s="203"/>
-      <c r="I14" s="197"/>
-      <c r="J14" s="197"/>
-      <c r="K14" s="197"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="212"/>
+      <c r="J14" s="212"/>
+      <c r="K14" s="212"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="196"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="205"/>
       <c r="E15" s="181">
         <v>10</v>
       </c>
@@ -3137,16 +3834,16 @@
       <c r="G15" s="183">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H15" s="203"/>
-      <c r="I15" s="197"/>
-      <c r="J15" s="197"/>
-      <c r="K15" s="197"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="212"/>
+      <c r="J15" s="212"/>
+      <c r="K15" s="212"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="196"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="205"/>
       <c r="E16" s="178">
         <v>11</v>
       </c>
@@ -3156,16 +3853,16 @@
       <c r="G16" s="180">
         <v>12.22</v>
       </c>
-      <c r="H16" s="203"/>
-      <c r="I16" s="197"/>
-      <c r="J16" s="197"/>
-      <c r="K16" s="197"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="197"/>
-      <c r="B17" s="197"/>
-      <c r="C17" s="197"/>
-      <c r="D17" s="196"/>
+      <c r="A17" s="212"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="205"/>
       <c r="E17" s="181">
         <v>12</v>
       </c>
@@ -3175,16 +3872,16 @@
       <c r="G17" s="183">
         <v>8.35</v>
       </c>
-      <c r="H17" s="203"/>
-      <c r="I17" s="197"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="197"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="197"/>
-      <c r="B18" s="197"/>
-      <c r="C18" s="197"/>
-      <c r="D18" s="196"/>
+      <c r="A18" s="212"/>
+      <c r="B18" s="212"/>
+      <c r="C18" s="212"/>
+      <c r="D18" s="205"/>
       <c r="E18" s="178">
         <v>13</v>
       </c>
@@ -3194,16 +3891,16 @@
       <c r="G18" s="180">
         <v>14.03</v>
       </c>
-      <c r="H18" s="203"/>
-      <c r="I18" s="197"/>
-      <c r="J18" s="197"/>
-      <c r="K18" s="197"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="197"/>
-      <c r="B19" s="197"/>
-      <c r="C19" s="197"/>
-      <c r="D19" s="196"/>
+      <c r="A19" s="212"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="212"/>
+      <c r="D19" s="205"/>
       <c r="E19" s="181">
         <v>12</v>
       </c>
@@ -3213,16 +3910,16 @@
       <c r="G19" s="183">
         <v>8.0299999999999994</v>
       </c>
-      <c r="H19" s="203"/>
-      <c r="I19" s="197"/>
-      <c r="J19" s="197"/>
-      <c r="K19" s="197"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="212"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="197"/>
-      <c r="B20" s="197"/>
-      <c r="C20" s="197"/>
-      <c r="D20" s="196"/>
+      <c r="A20" s="212"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="212"/>
+      <c r="D20" s="205"/>
       <c r="E20" s="178">
         <v>13</v>
       </c>
@@ -3232,16 +3929,16 @@
       <c r="G20" s="180">
         <v>16.2</v>
       </c>
-      <c r="H20" s="203"/>
-      <c r="I20" s="197"/>
-      <c r="J20" s="197"/>
-      <c r="K20" s="197"/>
+      <c r="H20" s="204"/>
+      <c r="I20" s="212"/>
+      <c r="J20" s="212"/>
+      <c r="K20" s="212"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="197"/>
-      <c r="B21" s="197"/>
-      <c r="C21" s="197"/>
-      <c r="D21" s="196"/>
+      <c r="A21" s="212"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="205"/>
       <c r="F21" s="182" t="s">
         <v>93</v>
       </c>
@@ -3249,10 +3946,10 @@
         <f>SUM(G6:G20)</f>
         <v>165.29999999999998</v>
       </c>
-      <c r="H21" s="203"/>
-      <c r="I21" s="197"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="197"/>
+      <c r="H21" s="204"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3274,7 +3971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -3290,19 +3987,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="206"/>
-      <c r="G1" s="207" t="s">
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="215"/>
+      <c r="G1" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="209"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="218"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="117" t="s">
@@ -3965,19 +4662,19 @@
       <c r="F28" s="121"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="204" t="s">
+      <c r="A31" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="205"/>
-      <c r="C31" s="205"/>
-      <c r="D31" s="205"/>
-      <c r="E31" s="206"/>
-      <c r="G31" s="207" t="s">
+      <c r="B31" s="214"/>
+      <c r="C31" s="214"/>
+      <c r="D31" s="214"/>
+      <c r="E31" s="215"/>
+      <c r="G31" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H31" s="208"/>
-      <c r="I31" s="208"/>
-      <c r="J31" s="209"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="217"/>
+      <c r="J31" s="218"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="117" t="s">
@@ -4871,19 +5568,19 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="204" t="s">
+      <c r="A80" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="205"/>
-      <c r="C80" s="205"/>
-      <c r="D80" s="205"/>
-      <c r="E80" s="206"/>
-      <c r="G80" s="207" t="s">
+      <c r="B80" s="214"/>
+      <c r="C80" s="214"/>
+      <c r="D80" s="214"/>
+      <c r="E80" s="215"/>
+      <c r="G80" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="208"/>
-      <c r="I80" s="208"/>
-      <c r="J80" s="209"/>
+      <c r="H80" s="217"/>
+      <c r="I80" s="217"/>
+      <c r="J80" s="218"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="117" t="s">
@@ -5455,7 +6152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5555,7 +6252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5567,13 +6264,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="209"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="218"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="122" t="s">
@@ -5715,7 +6412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -6122,7 +6819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -6131,13 +6828,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
@@ -6237,13 +6934,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="210" t="s">
+      <c r="A8" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="210"/>
-      <c r="C8" s="210"/>
-      <c r="D8" s="210"/>
-      <c r="E8" s="210"/>
+      <c r="B8" s="219"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="219"/>
+      <c r="E8" s="219"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="142" t="s">
@@ -6445,13 +7142,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="210" t="s">
+      <c r="A21" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="210"/>
-      <c r="C21" s="210"/>
-      <c r="D21" s="210"/>
-      <c r="E21" s="210"/>
+      <c r="B21" s="219"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
+      <c r="E21" s="219"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="142" t="s">
@@ -6563,13 +7260,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="216" t="s">
+      <c r="A30" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="216"/>
-      <c r="C30" s="216"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="216"/>
+      <c r="B30" s="225"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="150" t="s">
@@ -6606,13 +7303,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="213" t="s">
+      <c r="A33" s="222" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="214"/>
-      <c r="C33" s="214"/>
-      <c r="D33" s="214"/>
-      <c r="E33" s="215"/>
+      <c r="B33" s="223"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="224"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="150" t="s">
@@ -6707,13 +7404,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="211" t="s">
+      <c r="A42" s="220" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="211"/>
-      <c r="C42" s="211"/>
-      <c r="D42" s="211"/>
-      <c r="E42" s="211"/>
+      <c r="B42" s="220"/>
+      <c r="C42" s="220"/>
+      <c r="D42" s="220"/>
+      <c r="E42" s="220"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="162" t="s">
@@ -6847,13 +7544,13 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="211" t="s">
+      <c r="A51" s="220" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="211"/>
-      <c r="C51" s="211"/>
-      <c r="D51" s="211"/>
-      <c r="E51" s="211"/>
+      <c r="B51" s="220"/>
+      <c r="C51" s="220"/>
+      <c r="D51" s="220"/>
+      <c r="E51" s="220"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="162" t="s">
@@ -6970,13 +7667,13 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="211" t="s">
+      <c r="A59" s="220" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="211"/>
-      <c r="C59" s="211"/>
-      <c r="D59" s="211"/>
-      <c r="E59" s="211"/>
+      <c r="B59" s="220"/>
+      <c r="C59" s="220"/>
+      <c r="D59" s="220"/>
+      <c r="E59" s="220"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="162" t="s">
@@ -7088,13 +7785,13 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="189" t="s">
+      <c r="A68" s="197" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="189"/>
-      <c r="C68" s="189"/>
-      <c r="D68" s="189"/>
-      <c r="E68" s="189"/>
+      <c r="B68" s="197"/>
+      <c r="C68" s="197"/>
+      <c r="D68" s="197"/>
+      <c r="E68" s="197"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="123" t="s">
@@ -7131,13 +7828,13 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="212" t="s">
+      <c r="A73" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="212"/>
-      <c r="C73" s="212"/>
-      <c r="D73" s="212"/>
-      <c r="E73" s="212"/>
+      <c r="B73" s="221"/>
+      <c r="C73" s="221"/>
+      <c r="D73" s="221"/>
+      <c r="E73" s="221"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="156" t="s">
@@ -7220,13 +7917,13 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="212" t="s">
+      <c r="A79" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="212"/>
-      <c r="C79" s="212"/>
-      <c r="D79" s="212"/>
-      <c r="E79" s="212"/>
+      <c r="B79" s="221"/>
+      <c r="C79" s="221"/>
+      <c r="D79" s="221"/>
+      <c r="E79" s="221"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="156" t="s">
@@ -7275,13 +7972,13 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="210" t="s">
+      <c r="A85" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="210"/>
-      <c r="C85" s="210"/>
-      <c r="D85" s="210"/>
-      <c r="E85" s="210"/>
+      <c r="B85" s="219"/>
+      <c r="C85" s="219"/>
+      <c r="D85" s="219"/>
+      <c r="E85" s="219"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="142" t="s">
@@ -7318,13 +8015,13 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="210" t="s">
+      <c r="A88" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="210"/>
-      <c r="C88" s="210"/>
-      <c r="D88" s="210"/>
-      <c r="E88" s="210"/>
+      <c r="B88" s="219"/>
+      <c r="C88" s="219"/>
+      <c r="D88" s="219"/>
+      <c r="E88" s="219"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="142" t="s">
@@ -7390,13 +8087,13 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="210" t="s">
+      <c r="A93" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="210"/>
-      <c r="C93" s="210"/>
-      <c r="D93" s="210"/>
-      <c r="E93" s="210"/>
+      <c r="B93" s="219"/>
+      <c r="C93" s="219"/>
+      <c r="D93" s="219"/>
+      <c r="E93" s="219"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="142" t="s">
@@ -7509,25 +8206,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="197" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="198" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="192"/>
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="200"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -8304,18 +9001,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="201" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="202" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="194"/>
-      <c r="C2" s="194"/>
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -9477,6 +10174,752 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="206" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+    </row>
+    <row r="2" spans="1:11" s="195" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="193" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="209"/>
+      <c r="K2" s="194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="193">
+        <v>1</v>
+      </c>
+      <c r="B3" s="207" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="210"/>
+      <c r="K3" s="226">
+        <f>C13+C19+G15+K16</f>
+        <v>2125.2200000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="208"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="212"/>
+      <c r="E5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="212"/>
+      <c r="I5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="K5" s="177" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="180">
+        <v>114.46</v>
+      </c>
+      <c r="D6" s="212"/>
+      <c r="E6" s="178">
+        <v>1</v>
+      </c>
+      <c r="F6" s="178" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="180">
+        <v>73.849999999999994</v>
+      </c>
+      <c r="H6" s="212"/>
+      <c r="I6" s="178">
+        <v>1</v>
+      </c>
+      <c r="J6" s="178" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" s="180">
+        <v>127.87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="183">
+        <v>69</v>
+      </c>
+      <c r="D7" s="212"/>
+      <c r="E7" s="181">
+        <v>2</v>
+      </c>
+      <c r="F7" s="181" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="183">
+        <v>72.41</v>
+      </c>
+      <c r="H7" s="212"/>
+      <c r="I7" s="181">
+        <v>2</v>
+      </c>
+      <c r="J7" s="181" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" s="183">
+        <v>73.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="178">
+        <v>3</v>
+      </c>
+      <c r="B8" s="178" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="180">
+        <v>69.06</v>
+      </c>
+      <c r="D8" s="212"/>
+      <c r="E8" s="178">
+        <v>3</v>
+      </c>
+      <c r="F8" s="178" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="180">
+        <v>68.52</v>
+      </c>
+      <c r="H8" s="212"/>
+      <c r="I8" s="178">
+        <v>3</v>
+      </c>
+      <c r="J8" s="178" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="180">
+        <v>71.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="181" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="183">
+        <v>69.319999999999993</v>
+      </c>
+      <c r="D9" s="212"/>
+      <c r="E9" s="181">
+        <v>4</v>
+      </c>
+      <c r="F9" s="181" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="183">
+        <v>68.55</v>
+      </c>
+      <c r="H9" s="212"/>
+      <c r="I9" s="181">
+        <v>4</v>
+      </c>
+      <c r="J9" s="181" t="s">
+        <v>174</v>
+      </c>
+      <c r="K9" s="183">
+        <v>67.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="178">
+        <v>5</v>
+      </c>
+      <c r="B10" s="178" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="180">
+        <v>69.03</v>
+      </c>
+      <c r="D10" s="212"/>
+      <c r="E10" s="178">
+        <v>5</v>
+      </c>
+      <c r="F10" s="178" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="180">
+        <v>68.64</v>
+      </c>
+      <c r="H10" s="212"/>
+      <c r="I10" s="178">
+        <v>5</v>
+      </c>
+      <c r="J10" s="178" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" s="180">
+        <v>67.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
+        <v>6</v>
+      </c>
+      <c r="B11" s="181" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="183">
+        <v>68.28</v>
+      </c>
+      <c r="D11" s="212"/>
+      <c r="E11" s="181">
+        <v>6</v>
+      </c>
+      <c r="F11" s="181" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="183">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H11" s="212"/>
+      <c r="I11" s="181">
+        <v>6</v>
+      </c>
+      <c r="J11" s="181" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" s="183">
+        <v>68.180000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="178">
+        <v>7</v>
+      </c>
+      <c r="B12" s="178" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="180">
+        <v>137.83000000000001</v>
+      </c>
+      <c r="D12" s="212"/>
+      <c r="E12" s="178">
+        <v>7</v>
+      </c>
+      <c r="F12" s="178" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="180">
+        <v>67.58</v>
+      </c>
+      <c r="H12" s="212"/>
+      <c r="I12" s="178">
+        <v>7</v>
+      </c>
+      <c r="J12" s="178" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="180">
+        <v>68.010000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="182"/>
+      <c r="B13" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="183">
+        <f>SUM(C6:C12)</f>
+        <v>596.98</v>
+      </c>
+      <c r="D13" s="212"/>
+      <c r="E13" s="181">
+        <v>8</v>
+      </c>
+      <c r="F13" s="181" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="183">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H13" s="212"/>
+      <c r="I13" s="181">
+        <v>8</v>
+      </c>
+      <c r="J13" s="181" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="183">
+        <v>67.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="227"/>
+      <c r="B14" s="227"/>
+      <c r="C14" s="227"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="178">
+        <v>9</v>
+      </c>
+      <c r="F14" s="178" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="180">
+        <v>68.27</v>
+      </c>
+      <c r="H14" s="212"/>
+      <c r="I14" s="178">
+        <v>9</v>
+      </c>
+      <c r="J14" s="178" t="s">
+        <v>179</v>
+      </c>
+      <c r="K14" s="180">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="212"/>
+      <c r="F15" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="183">
+        <f>SUM(G6:G14)</f>
+        <v>624.7399999999999</v>
+      </c>
+      <c r="H15" s="212"/>
+      <c r="I15" s="181">
+        <v>10</v>
+      </c>
+      <c r="J15" s="181" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="183">
+        <v>67.81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="178">
+        <v>1</v>
+      </c>
+      <c r="B16" s="178" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="180">
+        <v>103.08</v>
+      </c>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="J16" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="K16" s="183">
+        <f>SUM(K6:K15)</f>
+        <v>747.40000000000009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="181">
+        <v>2</v>
+      </c>
+      <c r="B17" s="181" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="183">
+        <v>22.05</v>
+      </c>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="212"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="212"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="212"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="178">
+        <v>3</v>
+      </c>
+      <c r="B18" s="178" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="180">
+        <v>30.97</v>
+      </c>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="212"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
+      <c r="I18" s="212"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="212"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="182"/>
+      <c r="B19" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="183">
+        <f>SUM(C16:C18)</f>
+        <v>156.1</v>
+      </c>
+      <c r="D19" s="212"/>
+      <c r="E19" s="212"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="212"/>
+      <c r="I19" s="212"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="212"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="I17:K19"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="D5:D19"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="E16:G19"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="206" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+    </row>
+    <row r="2" spans="1:8" s="189" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="190" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="191" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="190">
+        <v>1</v>
+      </c>
+      <c r="B3" s="207" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="196" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="184">
+        <f>C12</f>
+        <v>1482.242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="203"/>
+      <c r="B4" s="203"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="204"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="180">
+        <f>191.78+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>262.21799999999996</v>
+      </c>
+      <c r="D6" s="204"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="183">
+        <f>146.45+59.6+0.942*13</f>
+        <v>218.29599999999999</v>
+      </c>
+      <c r="D7" s="204"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
+        <v>3</v>
+      </c>
+      <c r="B8" s="181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="183">
+        <f>158.69+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>229.12800000000001</v>
+      </c>
+      <c r="D8" s="204"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="183">
+        <f>145.8+59.6+0.942*13</f>
+        <v>217.64600000000002</v>
+      </c>
+      <c r="D9" s="204"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
+        <v>5</v>
+      </c>
+      <c r="B10" s="181" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="183">
+        <f>243.62+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>314.05799999999999</v>
+      </c>
+      <c r="D10" s="204"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="205"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="205"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
+        <v>6</v>
+      </c>
+      <c r="B11" s="178" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="180">
+        <f>146.65+59.6+22.4+0.942*13</f>
+        <v>240.89600000000002</v>
+      </c>
+      <c r="D11" s="204"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="205"/>
+      <c r="G11" s="205"/>
+      <c r="H11" s="205"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="182"/>
+      <c r="B12" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="183">
+        <f>SUM(C6:C11)</f>
+        <v>1482.242</v>
+      </c>
+      <c r="D12" s="204"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="205"/>
+      <c r="G12" s="205"/>
+      <c r="H12" s="205"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="D5:H12"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9493,39 +10936,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
     </row>
     <row r="2" spans="1:11" s="188" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="187" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="200" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="199" t="s">
+      <c r="B2" s="207" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="201" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="201"/>
+      <c r="J2" s="209"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -9534,38 +10977,38 @@
       <c r="A3" s="187">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="207" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="202" t="s">
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="210" t="s">
         <v>185</v>
       </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202" t="s">
+      <c r="H3" s="210"/>
+      <c r="I3" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="202"/>
+      <c r="J3" s="210"/>
       <c r="K3" s="184">
         <f>C7</f>
         <v>167.53</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="195"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
+      <c r="A4" s="208"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -9577,14 +11020,14 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="203"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="178">
@@ -9596,14 +11039,14 @@
       <c r="C6" s="180">
         <v>167.53</v>
       </c>
-      <c r="D6" s="203"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="196"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="182" t="s">
@@ -9616,14 +11059,14 @@
         <f>SUM(C6:C6)</f>
         <v>167.53</v>
       </c>
-      <c r="D7" s="203"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9640,662 +11083,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" customWidth="1"/>
-    <col min="9" max="10" width="8.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-    </row>
-    <row r="2" spans="1:11" s="185" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="186" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="200" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="199" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="201" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="201"/>
-      <c r="K2" s="173" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="186">
-        <v>1</v>
-      </c>
-      <c r="B3" s="200" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="202" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="202"/>
-      <c r="K3" s="184">
-        <f>C9</f>
-        <v>155.35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="217"/>
-      <c r="B4" s="217"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="203"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="178" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="180">
-        <v>102.83</v>
-      </c>
-      <c r="D6" s="203"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="196"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
-        <v>2</v>
-      </c>
-      <c r="B7" s="181" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="183">
-        <v>21.8</v>
-      </c>
-      <c r="D7" s="203"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="178">
-        <v>3</v>
-      </c>
-      <c r="B8" s="178" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="180">
-        <v>30.72</v>
-      </c>
-      <c r="D8" s="203"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
-      <c r="K8" s="196"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="182"/>
-      <c r="B9" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="183">
-        <f>SUM(C6:C8)</f>
-        <v>155.35</v>
-      </c>
-      <c r="D9" s="203"/>
-      <c r="E9" s="196"/>
-      <c r="F9" s="196"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="196"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="196"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="D5:K9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" customWidth="1"/>
-    <col min="9" max="10" width="8.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-    </row>
-    <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="200" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="199" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="199"/>
-      <c r="I2" s="201" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="201"/>
-      <c r="K2" s="173" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="172">
-        <v>1</v>
-      </c>
-      <c r="B3" s="200" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="202" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="202"/>
-      <c r="K3" s="184">
-        <f>C13+G15+K16</f>
-        <v>1966.37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="195" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="196"/>
-      <c r="E5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="197"/>
-      <c r="I5" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="J5" s="176" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="177" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="178" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="180">
-        <v>114.21</v>
-      </c>
-      <c r="D6" s="196"/>
-      <c r="E6" s="178">
-        <v>1</v>
-      </c>
-      <c r="F6" s="178" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="180">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="H6" s="197"/>
-      <c r="I6" s="178">
-        <v>1</v>
-      </c>
-      <c r="J6" s="178" t="s">
-        <v>171</v>
-      </c>
-      <c r="K6" s="180">
-        <v>127.87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
-        <v>2</v>
-      </c>
-      <c r="B7" s="181" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="183">
-        <v>68.75</v>
-      </c>
-      <c r="D7" s="196"/>
-      <c r="E7" s="181">
-        <v>2</v>
-      </c>
-      <c r="F7" s="181" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="183">
-        <v>72.16</v>
-      </c>
-      <c r="H7" s="197"/>
-      <c r="I7" s="181">
-        <v>2</v>
-      </c>
-      <c r="J7" s="181" t="s">
-        <v>172</v>
-      </c>
-      <c r="K7" s="183">
-        <v>73.17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="178">
-        <v>3</v>
-      </c>
-      <c r="B8" s="178" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="180">
-        <v>68.81</v>
-      </c>
-      <c r="D8" s="196"/>
-      <c r="E8" s="178">
-        <v>3</v>
-      </c>
-      <c r="F8" s="178" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="180">
-        <v>68.27</v>
-      </c>
-      <c r="H8" s="197"/>
-      <c r="I8" s="178">
-        <v>3</v>
-      </c>
-      <c r="J8" s="178" t="s">
-        <v>173</v>
-      </c>
-      <c r="K8" s="180">
-        <v>71.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="181">
-        <v>4</v>
-      </c>
-      <c r="B9" s="181" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="183">
-        <v>69.069999999999993</v>
-      </c>
-      <c r="D9" s="196"/>
-      <c r="E9" s="181">
-        <v>4</v>
-      </c>
-      <c r="F9" s="181" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="183">
-        <v>68.3</v>
-      </c>
-      <c r="H9" s="197"/>
-      <c r="I9" s="181">
-        <v>4</v>
-      </c>
-      <c r="J9" s="181" t="s">
-        <v>174</v>
-      </c>
-      <c r="K9" s="183">
-        <v>67.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="178">
-        <v>5</v>
-      </c>
-      <c r="B10" s="178" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="180">
-        <v>68.78</v>
-      </c>
-      <c r="D10" s="196"/>
-      <c r="E10" s="178">
-        <v>5</v>
-      </c>
-      <c r="F10" s="178" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="180">
-        <v>68.64</v>
-      </c>
-      <c r="H10" s="197"/>
-      <c r="I10" s="178">
-        <v>5</v>
-      </c>
-      <c r="J10" s="178" t="s">
-        <v>175</v>
-      </c>
-      <c r="K10" s="180">
-        <v>67.83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="181">
-        <v>6</v>
-      </c>
-      <c r="B11" s="181" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="183">
-        <v>68.03</v>
-      </c>
-      <c r="D11" s="196"/>
-      <c r="E11" s="181">
-        <v>6</v>
-      </c>
-      <c r="F11" s="181" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="183">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="H11" s="197"/>
-      <c r="I11" s="181">
-        <v>6</v>
-      </c>
-      <c r="J11" s="181" t="s">
-        <v>176</v>
-      </c>
-      <c r="K11" s="183">
-        <v>68.180000000000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="178">
-        <v>7</v>
-      </c>
-      <c r="B12" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="180">
-        <v>137.58000000000001</v>
-      </c>
-      <c r="D12" s="196"/>
-      <c r="E12" s="178">
-        <v>7</v>
-      </c>
-      <c r="F12" s="178" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="180">
-        <v>67.58</v>
-      </c>
-      <c r="H12" s="197"/>
-      <c r="I12" s="178">
-        <v>7</v>
-      </c>
-      <c r="J12" s="178" t="s">
-        <v>177</v>
-      </c>
-      <c r="K12" s="180">
-        <v>68.010000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="182"/>
-      <c r="B13" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="183">
-        <f>SUM(C6:C12)</f>
-        <v>595.23</v>
-      </c>
-      <c r="D13" s="196"/>
-      <c r="E13" s="181">
-        <v>8</v>
-      </c>
-      <c r="F13" s="181" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="183">
-        <v>68.459999999999994</v>
-      </c>
-      <c r="H13" s="197"/>
-      <c r="I13" s="181">
-        <v>8</v>
-      </c>
-      <c r="J13" s="181" t="s">
-        <v>178</v>
-      </c>
-      <c r="K13" s="183">
-        <v>67.14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="178">
-        <v>9</v>
-      </c>
-      <c r="F14" s="178" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="180">
-        <v>68.27</v>
-      </c>
-      <c r="H14" s="197"/>
-      <c r="I14" s="178">
-        <v>9</v>
-      </c>
-      <c r="J14" s="178" t="s">
-        <v>179</v>
-      </c>
-      <c r="K14" s="180">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="196"/>
-      <c r="F15" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="183">
-        <f>SUM(G6:G14)</f>
-        <v>623.7399999999999</v>
-      </c>
-      <c r="H15" s="197"/>
-      <c r="I15" s="181">
-        <v>10</v>
-      </c>
-      <c r="J15" s="181" t="s">
-        <v>180</v>
-      </c>
-      <c r="K15" s="183">
-        <v>67.81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="197"/>
-      <c r="G16" s="197"/>
-      <c r="H16" s="197"/>
-      <c r="J16" s="182" t="s">
-        <v>93</v>
-      </c>
-      <c r="K16" s="183">
-        <f>SUM(K6:K15)</f>
-        <v>747.40000000000009</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A14:C16"/>
-    <mergeCell ref="D5:D16"/>
-    <mergeCell ref="H5:H16"/>
-    <mergeCell ref="E16:G16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/school_lublino/ceilling/vor_lublino_ceiling.xlsx
+++ b/school_lublino/ceilling/vor_lublino_ceiling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="5532" windowHeight="3396" tabRatio="790" firstSheet="6" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="5532" windowHeight="3396" tabRatio="790" firstSheet="6" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" state="hidden" r:id="rId1"/>
@@ -19,24 +19,25 @@
     <sheet name="1эт спец" sheetId="11" state="hidden" r:id="rId5"/>
     <sheet name="Вор2Вып" sheetId="12" state="hidden" r:id="rId6"/>
     <sheet name="9.3П8" sheetId="24" r:id="rId7"/>
-    <sheet name="7.1КрсИнж" sheetId="23" r:id="rId8"/>
-    <sheet name="6.5П7,10 (2)" sheetId="22" r:id="rId9"/>
-    <sheet name="6.4П8" sheetId="21" r:id="rId10"/>
-    <sheet name="6.3П8" sheetId="20" r:id="rId11"/>
-    <sheet name="6.2П7,10" sheetId="19" r:id="rId12"/>
-    <sheet name="6.1П9" sheetId="18" r:id="rId13"/>
-    <sheet name="Общий" sheetId="13" r:id="rId14"/>
-    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId16"/>
-    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId17"/>
-    <sheet name="ПокрПом" sheetId="16" r:id="rId18"/>
+    <sheet name="7.2КрсИнж" sheetId="25" r:id="rId8"/>
+    <sheet name="7.1КрсИнж" sheetId="23" r:id="rId9"/>
+    <sheet name="6.5П7,10 (2)" sheetId="22" r:id="rId10"/>
+    <sheet name="6.4П8" sheetId="21" r:id="rId11"/>
+    <sheet name="6.3П8" sheetId="20" r:id="rId12"/>
+    <sheet name="6.2П7,10" sheetId="19" r:id="rId13"/>
+    <sheet name="6.1П9" sheetId="18" r:id="rId14"/>
+    <sheet name="Общий" sheetId="13" r:id="rId15"/>
+    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId16"/>
+    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId17"/>
+    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId18"/>
+    <sheet name="ПокрПом" sheetId="16" r:id="rId19"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="196">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -604,9 +605,38 @@
 СКБ / окраска потолков /</t>
   </si>
   <si>
+    <t>Инж. Ком
+Объем, м²</t>
+  </si>
+  <si>
+    <t>Итог
+Объем, м²</t>
+  </si>
+  <si>
+    <t>1.045</t>
+  </si>
+  <si>
+    <t>1.046</t>
+  </si>
+  <si>
     <t>Окраска потолка/
 окраска инженерных
-коммуникации / Тип П-6</t>
+коммуникации /</t>
+  </si>
+  <si>
+    <t>1.053</t>
+  </si>
+  <si>
+    <t>Потолок
+Объем, м²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">окраска инженерных
+коммуникации </t>
+  </si>
+  <si>
+    <t>окраска инженерных
+коммуникации /</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1356,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1861,9 +1891,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1882,6 +1925,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1891,27 +1952,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1930,31 +1973,63 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2606,6 +2681,173 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="5" max="6" width="8.77734375" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="1.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" customWidth="1"/>
+    <col min="10" max="10" width="2.88671875" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="210" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+    </row>
+    <row r="2" spans="1:11" s="188" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="212"/>
+      <c r="K2" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="187">
+        <v>1</v>
+      </c>
+      <c r="B3" s="211" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="213"/>
+      <c r="K3" s="184">
+        <f>C7</f>
+        <v>167.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="209"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="177" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="215"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="179" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="180">
+        <v>167.53</v>
+      </c>
+      <c r="D6" s="215"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="182" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="183">
+        <f>SUM(C6:C6)</f>
+        <v>167.53</v>
+      </c>
+      <c r="D7" s="215"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:K7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2621,39 +2863,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
     </row>
     <row r="2" spans="1:11" s="185" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -2662,38 +2904,38 @@
       <c r="A3" s="186">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
+      <c r="J3" s="213"/>
       <c r="K3" s="184">
         <f>C9</f>
         <v>155.35</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="203"/>
-      <c r="B4" s="203"/>
-      <c r="C4" s="203"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="203"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="203"/>
+      <c r="A4" s="214"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
+      <c r="K4" s="214"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -2705,14 +2947,14 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="178">
@@ -2724,14 +2966,14 @@
       <c r="C6" s="180">
         <v>102.83</v>
       </c>
-      <c r="D6" s="204"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="181">
@@ -2743,14 +2985,14 @@
       <c r="C7" s="183">
         <v>21.8</v>
       </c>
-      <c r="D7" s="204"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="178">
@@ -2762,14 +3004,14 @@
       <c r="C8" s="180">
         <v>30.72</v>
       </c>
-      <c r="D8" s="204"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="182"/>
@@ -2780,14 +3022,14 @@
         <f>SUM(C6:C8)</f>
         <v>155.35</v>
       </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="205"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2806,7 +3048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2823,39 +3065,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -2864,40 +3106,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
+      <c r="J3" s="213"/>
       <c r="K3" s="184">
         <f>C13+G15+K16</f>
         <v>1966.37</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="209" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -2909,7 +3151,7 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="205"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="175" t="s">
         <v>0</v>
       </c>
@@ -2919,7 +3161,7 @@
       <c r="G5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="212"/>
+      <c r="H5" s="208"/>
       <c r="I5" s="175" t="s">
         <v>0</v>
       </c>
@@ -2940,7 +3182,7 @@
       <c r="C6" s="180">
         <v>114.21</v>
       </c>
-      <c r="D6" s="205"/>
+      <c r="D6" s="216"/>
       <c r="E6" s="178">
         <v>1</v>
       </c>
@@ -2950,7 +3192,7 @@
       <c r="G6" s="180">
         <v>73.599999999999994</v>
       </c>
-      <c r="H6" s="212"/>
+      <c r="H6" s="208"/>
       <c r="I6" s="178">
         <v>1</v>
       </c>
@@ -2971,7 +3213,7 @@
       <c r="C7" s="183">
         <v>68.75</v>
       </c>
-      <c r="D7" s="205"/>
+      <c r="D7" s="216"/>
       <c r="E7" s="181">
         <v>2</v>
       </c>
@@ -2981,7 +3223,7 @@
       <c r="G7" s="183">
         <v>72.16</v>
       </c>
-      <c r="H7" s="212"/>
+      <c r="H7" s="208"/>
       <c r="I7" s="181">
         <v>2</v>
       </c>
@@ -3002,7 +3244,7 @@
       <c r="C8" s="180">
         <v>68.81</v>
       </c>
-      <c r="D8" s="205"/>
+      <c r="D8" s="216"/>
       <c r="E8" s="178">
         <v>3</v>
       </c>
@@ -3012,7 +3254,7 @@
       <c r="G8" s="180">
         <v>68.27</v>
       </c>
-      <c r="H8" s="212"/>
+      <c r="H8" s="208"/>
       <c r="I8" s="178">
         <v>3</v>
       </c>
@@ -3033,7 +3275,7 @@
       <c r="C9" s="183">
         <v>69.069999999999993</v>
       </c>
-      <c r="D9" s="205"/>
+      <c r="D9" s="216"/>
       <c r="E9" s="181">
         <v>4</v>
       </c>
@@ -3043,7 +3285,7 @@
       <c r="G9" s="183">
         <v>68.3</v>
       </c>
-      <c r="H9" s="212"/>
+      <c r="H9" s="208"/>
       <c r="I9" s="181">
         <v>4</v>
       </c>
@@ -3064,7 +3306,7 @@
       <c r="C10" s="180">
         <v>68.78</v>
       </c>
-      <c r="D10" s="205"/>
+      <c r="D10" s="216"/>
       <c r="E10" s="178">
         <v>5</v>
       </c>
@@ -3074,7 +3316,7 @@
       <c r="G10" s="180">
         <v>68.64</v>
       </c>
-      <c r="H10" s="212"/>
+      <c r="H10" s="208"/>
       <c r="I10" s="178">
         <v>5</v>
       </c>
@@ -3095,7 +3337,7 @@
       <c r="C11" s="183">
         <v>68.03</v>
       </c>
-      <c r="D11" s="205"/>
+      <c r="D11" s="216"/>
       <c r="E11" s="181">
         <v>6</v>
       </c>
@@ -3105,7 +3347,7 @@
       <c r="G11" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H11" s="212"/>
+      <c r="H11" s="208"/>
       <c r="I11" s="181">
         <v>6</v>
       </c>
@@ -3126,7 +3368,7 @@
       <c r="C12" s="180">
         <v>137.58000000000001</v>
       </c>
-      <c r="D12" s="205"/>
+      <c r="D12" s="216"/>
       <c r="E12" s="178">
         <v>7</v>
       </c>
@@ -3136,7 +3378,7 @@
       <c r="G12" s="180">
         <v>67.58</v>
       </c>
-      <c r="H12" s="212"/>
+      <c r="H12" s="208"/>
       <c r="I12" s="178">
         <v>7</v>
       </c>
@@ -3156,7 +3398,7 @@
         <f>SUM(C6:C12)</f>
         <v>595.23</v>
       </c>
-      <c r="D13" s="205"/>
+      <c r="D13" s="216"/>
       <c r="E13" s="181">
         <v>8</v>
       </c>
@@ -3166,7 +3408,7 @@
       <c r="G13" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H13" s="212"/>
+      <c r="H13" s="208"/>
       <c r="I13" s="181">
         <v>8</v>
       </c>
@@ -3178,10 +3420,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="211"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="205"/>
+      <c r="A14" s="217"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="216"/>
       <c r="E14" s="178">
         <v>9</v>
       </c>
@@ -3191,7 +3433,7 @@
       <c r="G14" s="180">
         <v>68.27</v>
       </c>
-      <c r="H14" s="212"/>
+      <c r="H14" s="208"/>
       <c r="I14" s="178">
         <v>9</v>
       </c>
@@ -3203,10 +3445,10 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="205"/>
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="216"/>
       <c r="F15" s="182" t="s">
         <v>93</v>
       </c>
@@ -3214,7 +3456,7 @@
         <f>SUM(G6:G14)</f>
         <v>623.7399999999999</v>
       </c>
-      <c r="H15" s="212"/>
+      <c r="H15" s="208"/>
       <c r="I15" s="181">
         <v>10</v>
       </c>
@@ -3226,14 +3468,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="208"/>
+      <c r="H16" s="208"/>
       <c r="J16" s="182" t="s">
         <v>93</v>
       </c>
@@ -3244,6 +3486,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A14:C16"/>
+    <mergeCell ref="D5:D16"/>
+    <mergeCell ref="H5:H16"/>
+    <mergeCell ref="E16:G16"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -3251,18 +3498,13 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A14:C16"/>
-    <mergeCell ref="D5:D16"/>
-    <mergeCell ref="H5:H16"/>
-    <mergeCell ref="E16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3279,39 +3521,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -3320,40 +3562,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
+      <c r="J3" s="213"/>
       <c r="K3" s="184">
         <f>C9</f>
         <v>292.98</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="209" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -3365,14 +3607,14 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="178">
@@ -3384,14 +3626,14 @@
       <c r="C6" s="180">
         <v>219.5</v>
       </c>
-      <c r="D6" s="204"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="181">
@@ -3403,14 +3645,14 @@
       <c r="C7" s="183">
         <v>59.48</v>
       </c>
-      <c r="D7" s="204"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
+      <c r="D7" s="215"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="178">
@@ -3422,14 +3664,14 @@
       <c r="C8" s="180">
         <v>14</v>
       </c>
-      <c r="D8" s="204"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
+      <c r="D8" s="215"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="182" t="s">
@@ -3442,14 +3684,14 @@
         <f>SUM(C6:C8)</f>
         <v>292.98</v>
       </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="205"/>
+      <c r="D9" s="215"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3468,7 +3710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3484,39 +3726,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
     </row>
     <row r="2" spans="1:11" s="174" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="173" t="s">
         <v>6</v>
       </c>
@@ -3525,40 +3767,40 @@
       <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
         <v>150</v>
       </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
+      <c r="J3" s="213"/>
       <c r="K3" s="184">
         <f>C10+G21+K10</f>
         <v>258.09999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="209" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -3570,7 +3812,7 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="205"/>
+      <c r="D5" s="216"/>
       <c r="E5" s="175" t="s">
         <v>0</v>
       </c>
@@ -3580,7 +3822,7 @@
       <c r="G5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="204"/>
+      <c r="H5" s="215"/>
       <c r="I5" s="175" t="s">
         <v>0</v>
       </c>
@@ -3601,7 +3843,7 @@
       <c r="C6" s="180">
         <v>17.2</v>
       </c>
-      <c r="D6" s="205"/>
+      <c r="D6" s="216"/>
       <c r="E6" s="178">
         <v>1</v>
       </c>
@@ -3611,7 +3853,7 @@
       <c r="G6" s="180">
         <v>17.2</v>
       </c>
-      <c r="H6" s="204"/>
+      <c r="H6" s="215"/>
       <c r="I6" s="178">
         <v>1</v>
       </c>
@@ -3632,7 +3874,7 @@
       <c r="C7" s="183">
         <v>20.7</v>
       </c>
-      <c r="D7" s="205"/>
+      <c r="D7" s="216"/>
       <c r="E7" s="181">
         <v>2</v>
       </c>
@@ -3642,7 +3884,7 @@
       <c r="G7" s="183">
         <v>20.7</v>
       </c>
-      <c r="H7" s="204"/>
+      <c r="H7" s="215"/>
       <c r="I7" s="181">
         <v>2</v>
       </c>
@@ -3663,7 +3905,7 @@
       <c r="C8" s="180">
         <v>5.5</v>
       </c>
-      <c r="D8" s="205"/>
+      <c r="D8" s="216"/>
       <c r="E8" s="178">
         <v>3</v>
       </c>
@@ -3673,7 +3915,7 @@
       <c r="G8" s="180">
         <v>5.5</v>
       </c>
-      <c r="H8" s="204"/>
+      <c r="H8" s="215"/>
       <c r="I8" s="178">
         <v>3</v>
       </c>
@@ -3694,7 +3936,7 @@
       <c r="C9" s="183">
         <v>3</v>
       </c>
-      <c r="D9" s="205"/>
+      <c r="D9" s="216"/>
       <c r="E9" s="181">
         <v>4</v>
       </c>
@@ -3704,7 +3946,7 @@
       <c r="G9" s="183">
         <v>3</v>
       </c>
-      <c r="H9" s="204"/>
+      <c r="H9" s="215"/>
       <c r="I9" s="181">
         <v>4</v>
       </c>
@@ -3724,7 +3966,7 @@
         <f>SUM(C6:C9)</f>
         <v>46.4</v>
       </c>
-      <c r="D10" s="205"/>
+      <c r="D10" s="216"/>
       <c r="E10" s="178">
         <v>5</v>
       </c>
@@ -3734,7 +3976,7 @@
       <c r="G10" s="180">
         <v>6.08</v>
       </c>
-      <c r="H10" s="204"/>
+      <c r="H10" s="215"/>
       <c r="I10" s="178"/>
       <c r="J10" s="182" t="s">
         <v>93</v>
@@ -3745,10 +3987,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="211"/>
-      <c r="B11" s="211"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="205"/>
+      <c r="A11" s="217"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
+      <c r="D11" s="216"/>
       <c r="E11" s="181">
         <v>6</v>
       </c>
@@ -3758,16 +4000,16 @@
       <c r="G11" s="183">
         <v>12.15</v>
       </c>
-      <c r="H11" s="204"/>
-      <c r="I11" s="211"/>
-      <c r="J11" s="211"/>
-      <c r="K11" s="211"/>
+      <c r="H11" s="215"/>
+      <c r="I11" s="217"/>
+      <c r="J11" s="217"/>
+      <c r="K11" s="217"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="212"/>
-      <c r="B12" s="212"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="205"/>
+      <c r="A12" s="208"/>
+      <c r="B12" s="208"/>
+      <c r="C12" s="208"/>
+      <c r="D12" s="216"/>
       <c r="E12" s="178">
         <v>7</v>
       </c>
@@ -3777,16 +4019,16 @@
       <c r="G12" s="180">
         <v>10.67</v>
       </c>
-      <c r="H12" s="204"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="212"/>
-      <c r="K12" s="212"/>
+      <c r="H12" s="215"/>
+      <c r="I12" s="208"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="208"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="212"/>
-      <c r="B13" s="212"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="205"/>
+      <c r="A13" s="208"/>
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="216"/>
       <c r="E13" s="181">
         <v>8</v>
       </c>
@@ -3796,16 +4038,16 @@
       <c r="G13" s="183">
         <v>8.81</v>
       </c>
-      <c r="H13" s="204"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
+      <c r="H13" s="215"/>
+      <c r="I13" s="208"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="208"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="212"/>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="205"/>
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="216"/>
       <c r="E14" s="178">
         <v>9</v>
       </c>
@@ -3815,16 +4057,16 @@
       <c r="G14" s="180">
         <v>14.23</v>
       </c>
-      <c r="H14" s="204"/>
-      <c r="I14" s="212"/>
-      <c r="J14" s="212"/>
-      <c r="K14" s="212"/>
+      <c r="H14" s="215"/>
+      <c r="I14" s="208"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="208"/>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="205"/>
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="216"/>
       <c r="E15" s="181">
         <v>10</v>
       </c>
@@ -3834,16 +4076,16 @@
       <c r="G15" s="183">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H15" s="204"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="212"/>
-      <c r="K15" s="212"/>
+      <c r="H15" s="215"/>
+      <c r="I15" s="208"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="208"/>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="205"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="216"/>
       <c r="E16" s="178">
         <v>11</v>
       </c>
@@ -3853,16 +4095,16 @@
       <c r="G16" s="180">
         <v>12.22</v>
       </c>
-      <c r="H16" s="204"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="212"/>
+      <c r="H16" s="215"/>
+      <c r="I16" s="208"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="208"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="212"/>
-      <c r="B17" s="212"/>
-      <c r="C17" s="212"/>
-      <c r="D17" s="205"/>
+      <c r="A17" s="208"/>
+      <c r="B17" s="208"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="216"/>
       <c r="E17" s="181">
         <v>12</v>
       </c>
@@ -3872,16 +4114,16 @@
       <c r="G17" s="183">
         <v>8.35</v>
       </c>
-      <c r="H17" s="204"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="212"/>
+      <c r="H17" s="215"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="212"/>
-      <c r="B18" s="212"/>
-      <c r="C18" s="212"/>
-      <c r="D18" s="205"/>
+      <c r="A18" s="208"/>
+      <c r="B18" s="208"/>
+      <c r="C18" s="208"/>
+      <c r="D18" s="216"/>
       <c r="E18" s="178">
         <v>13</v>
       </c>
@@ -3891,16 +4133,16 @@
       <c r="G18" s="180">
         <v>14.03</v>
       </c>
-      <c r="H18" s="204"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
+      <c r="H18" s="215"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="212"/>
-      <c r="B19" s="212"/>
-      <c r="C19" s="212"/>
-      <c r="D19" s="205"/>
+      <c r="A19" s="208"/>
+      <c r="B19" s="208"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="216"/>
       <c r="E19" s="181">
         <v>12</v>
       </c>
@@ -3910,16 +4152,16 @@
       <c r="G19" s="183">
         <v>8.0299999999999994</v>
       </c>
-      <c r="H19" s="204"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="212"/>
+      <c r="H19" s="215"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="212"/>
-      <c r="B20" s="212"/>
-      <c r="C20" s="212"/>
-      <c r="D20" s="205"/>
+      <c r="A20" s="208"/>
+      <c r="B20" s="208"/>
+      <c r="C20" s="208"/>
+      <c r="D20" s="216"/>
       <c r="E20" s="178">
         <v>13</v>
       </c>
@@ -3929,16 +4171,16 @@
       <c r="G20" s="180">
         <v>16.2</v>
       </c>
-      <c r="H20" s="204"/>
-      <c r="I20" s="212"/>
-      <c r="J20" s="212"/>
-      <c r="K20" s="212"/>
+      <c r="H20" s="215"/>
+      <c r="I20" s="208"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="208"/>
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="212"/>
-      <c r="B21" s="212"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="205"/>
+      <c r="A21" s="208"/>
+      <c r="B21" s="208"/>
+      <c r="C21" s="208"/>
+      <c r="D21" s="216"/>
       <c r="F21" s="182" t="s">
         <v>93</v>
       </c>
@@ -3946,10 +4188,10 @@
         <f>SUM(G6:G20)</f>
         <v>165.29999999999998</v>
       </c>
-      <c r="H21" s="204"/>
-      <c r="I21" s="212"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="212"/>
+      <c r="H21" s="215"/>
+      <c r="I21" s="208"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3971,12 +4213,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -3987,19 +4229,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
-      <c r="G1" s="216" t="s">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="220"/>
+      <c r="G1" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="218"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="223"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="117" t="s">
@@ -4662,19 +4904,19 @@
       <c r="F28" s="121"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="213" t="s">
+      <c r="A31" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="214"/>
-      <c r="C31" s="214"/>
-      <c r="D31" s="214"/>
-      <c r="E31" s="215"/>
-      <c r="G31" s="216" t="s">
+      <c r="B31" s="219"/>
+      <c r="C31" s="219"/>
+      <c r="D31" s="219"/>
+      <c r="E31" s="220"/>
+      <c r="G31" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="H31" s="217"/>
-      <c r="I31" s="217"/>
-      <c r="J31" s="218"/>
+      <c r="H31" s="222"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="223"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="117" t="s">
@@ -5568,19 +5810,19 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="213" t="s">
+      <c r="A80" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="214"/>
-      <c r="C80" s="214"/>
-      <c r="D80" s="214"/>
-      <c r="E80" s="215"/>
-      <c r="G80" s="216" t="s">
+      <c r="B80" s="219"/>
+      <c r="C80" s="219"/>
+      <c r="D80" s="219"/>
+      <c r="E80" s="220"/>
+      <c r="G80" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="217"/>
-      <c r="I80" s="217"/>
-      <c r="J80" s="218"/>
+      <c r="H80" s="222"/>
+      <c r="I80" s="222"/>
+      <c r="J80" s="223"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="117" t="s">
@@ -5956,7 +6198,7 @@
         <v>129.68</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>16</v>
       </c>
@@ -5973,7 +6215,7 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>17</v>
       </c>
@@ -5990,7 +6232,7 @@
         <v>21.12</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>18</v>
       </c>
@@ -6007,7 +6249,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>19</v>
       </c>
@@ -6024,7 +6266,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>20</v>
       </c>
@@ -6041,7 +6283,7 @@
         <v>15.62</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>21</v>
       </c>
@@ -6058,7 +6300,7 @@
         <v>140.80000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>22</v>
       </c>
@@ -6075,7 +6317,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>23</v>
       </c>
@@ -6092,7 +6334,7 @@
         <v>15.07</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>24</v>
       </c>
@@ -6109,7 +6351,7 @@
         <v>13.16</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>25</v>
       </c>
@@ -6133,8 +6375,295 @@
         <v>309.60999999999996</v>
       </c>
     </row>
+    <row r="111" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G111" s="210" t="s">
+        <v>108</v>
+      </c>
+      <c r="H111" s="210"/>
+      <c r="I111" s="210"/>
+      <c r="J111" s="210"/>
+      <c r="K111" s="210"/>
+      <c r="L111" s="210"/>
+      <c r="M111" s="210"/>
+      <c r="N111" s="210"/>
+    </row>
+    <row r="112" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G112" s="196" t="s">
+        <v>0</v>
+      </c>
+      <c r="H112" s="234" t="s">
+        <v>1</v>
+      </c>
+      <c r="I112" s="235"/>
+      <c r="J112" s="236"/>
+      <c r="K112" s="237" t="s">
+        <v>148</v>
+      </c>
+      <c r="L112" s="238"/>
+      <c r="M112" s="197" t="s">
+        <v>12</v>
+      </c>
+      <c r="N112" s="173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G113" s="196">
+        <v>1</v>
+      </c>
+      <c r="H113" s="234" t="s">
+        <v>186</v>
+      </c>
+      <c r="I113" s="235"/>
+      <c r="J113" s="236"/>
+      <c r="K113" s="239" t="s">
+        <v>191</v>
+      </c>
+      <c r="L113" s="240"/>
+      <c r="M113" s="198" t="s">
+        <v>42</v>
+      </c>
+      <c r="N113" s="184">
+        <f>K124</f>
+        <v>2207.5182500000001</v>
+      </c>
+    </row>
+    <row r="114" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G114" s="214"/>
+      <c r="H114" s="214"/>
+      <c r="I114" s="214"/>
+      <c r="J114" s="214"/>
+      <c r="K114" s="214"/>
+      <c r="L114" s="214"/>
+      <c r="M114" s="214"/>
+      <c r="N114" s="214"/>
+    </row>
+    <row r="115" spans="7:14" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="G115" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="H115" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="I115" s="231" t="s">
+        <v>193</v>
+      </c>
+      <c r="J115" s="231" t="s">
+        <v>187</v>
+      </c>
+      <c r="K115" s="231" t="s">
+        <v>188</v>
+      </c>
+      <c r="L115" s="215"/>
+      <c r="M115" s="216"/>
+      <c r="N115" s="216"/>
+    </row>
+    <row r="116" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G116" s="232">
+        <v>1</v>
+      </c>
+      <c r="H116" s="232" t="s">
+        <v>192</v>
+      </c>
+      <c r="I116" s="233">
+        <v>436.5</v>
+      </c>
+      <c r="J116" s="233">
+        <f>((0.8+0.5*2)*19.3+(0.8+0.5*2)*10.9+(0.6+0.3*2)*8.1+0.25*3.14*28.1+(0.4+0.2*2)*7.3+0.1*2*30)*2</f>
+        <v>195.95699999999999</v>
+      </c>
+      <c r="K116" s="233">
+        <f>I116+J116</f>
+        <v>632.45699999999999</v>
+      </c>
+      <c r="L116" s="215"/>
+      <c r="M116" s="216"/>
+      <c r="N116" s="216"/>
+    </row>
+    <row r="117" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G117" s="232">
+        <v>2</v>
+      </c>
+      <c r="H117" s="232" t="s">
+        <v>190</v>
+      </c>
+      <c r="I117" s="233">
+        <v>153.1</v>
+      </c>
+      <c r="J117" s="233">
+        <f>((17.4+21+23)*3.14*0.25+0.1*2*30)*2</f>
+        <v>108.398</v>
+      </c>
+      <c r="K117" s="233">
+        <f t="shared" ref="K117:K123" si="1">I117+J117</f>
+        <v>261.49799999999999</v>
+      </c>
+      <c r="L117" s="215"/>
+      <c r="M117" s="216"/>
+      <c r="N117" s="216"/>
+    </row>
+    <row r="118" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G118" s="232">
+        <v>3</v>
+      </c>
+      <c r="H118" s="232" t="s">
+        <v>189</v>
+      </c>
+      <c r="I118" s="233">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="J118" s="233">
+        <f>(2*4.7)*3.14*0.25+(0.6+0.3*2)*19.3+(0.8+0.5*2)*5.5+3.14*0.25*17.4+(0.8+0.6*2)*12.3+(0.5+0.3*2)*16.4+(0.5+0.3*2)*18.1+0.1*2*30</f>
+        <v>122.648</v>
+      </c>
+      <c r="K118" s="233">
+        <f t="shared" si="1"/>
+        <v>281.94799999999998</v>
+      </c>
+      <c r="L118" s="215"/>
+      <c r="M118" s="216"/>
+      <c r="N118" s="216"/>
+    </row>
+    <row r="119" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G119" s="232">
+        <v>4</v>
+      </c>
+      <c r="H119" s="181" t="s">
+        <v>32</v>
+      </c>
+      <c r="I119" s="183">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="J119" s="183">
+        <f>(0.2+0.2*2)*16.9+3.14*0.125*23.8+(0.4+0.2*2)*16.2+(0.8+0.5*2)*7.4+0.1*2*30</f>
+        <v>51.761500000000005</v>
+      </c>
+      <c r="K119" s="233">
+        <f t="shared" si="1"/>
+        <v>130.16150000000002</v>
+      </c>
+      <c r="L119" s="215"/>
+      <c r="M119" s="216"/>
+      <c r="N119" s="216"/>
+    </row>
+    <row r="120" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G120" s="232">
+        <v>5</v>
+      </c>
+      <c r="H120" s="181" t="s">
+        <v>24</v>
+      </c>
+      <c r="I120" s="183">
+        <v>169.4</v>
+      </c>
+      <c r="J120" s="183">
+        <f>((0.8+0.5*2)*14.1+0.1*2*30)*2</f>
+        <v>62.76</v>
+      </c>
+      <c r="K120" s="233">
+        <f t="shared" si="1"/>
+        <v>232.16</v>
+      </c>
+      <c r="L120" s="215"/>
+      <c r="M120" s="216"/>
+      <c r="N120" s="216"/>
+    </row>
+    <row r="121" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G121" s="232">
+        <v>6</v>
+      </c>
+      <c r="H121" s="181" t="s">
+        <v>43</v>
+      </c>
+      <c r="I121" s="183">
+        <v>31.4</v>
+      </c>
+      <c r="J121" s="183">
+        <f>3.14*0.125*17.9</f>
+        <v>7.0257499999999995</v>
+      </c>
+      <c r="K121" s="233">
+        <f t="shared" si="1"/>
+        <v>38.425750000000001</v>
+      </c>
+      <c r="L121" s="215"/>
+      <c r="M121" s="216"/>
+      <c r="N121" s="216"/>
+    </row>
+    <row r="122" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G122" s="232">
+        <v>7</v>
+      </c>
+      <c r="H122" s="181" t="s">
+        <v>55</v>
+      </c>
+      <c r="I122" s="183">
+        <v>241.1</v>
+      </c>
+      <c r="J122" s="183">
+        <f>((0.8+0.5*2)*14.1+0.1*2*30+(0.8+0.5*2)*8.5+3.14*0.125*7.2)*3</f>
+        <v>148.518</v>
+      </c>
+      <c r="K122" s="233">
+        <f t="shared" si="1"/>
+        <v>389.61799999999999</v>
+      </c>
+      <c r="L122" s="215"/>
+      <c r="M122" s="216"/>
+      <c r="N122" s="216"/>
+    </row>
+    <row r="123" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G123" s="232">
+        <v>8</v>
+      </c>
+      <c r="H123" s="181" t="s">
+        <v>56</v>
+      </c>
+      <c r="I123" s="183">
+        <v>136.69999999999999</v>
+      </c>
+      <c r="J123" s="183">
+        <f>((0.8+0.5*2)*7.5+0.1*2*30+(0.4+0.2*2)*10.7+(0.4+0.2*2)*17.2)*2.5</f>
+        <v>104.55</v>
+      </c>
+      <c r="K123" s="233">
+        <f t="shared" si="1"/>
+        <v>241.25</v>
+      </c>
+      <c r="L123" s="215"/>
+      <c r="M123" s="216"/>
+      <c r="N123" s="216"/>
+    </row>
+    <row r="124" spans="7:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G124" s="182"/>
+      <c r="H124" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="I124" s="183">
+        <f>SUM(I116:I123)</f>
+        <v>1405.9</v>
+      </c>
+      <c r="J124" s="183">
+        <f t="shared" ref="J124:K124" si="2">SUM(J116:J123)</f>
+        <v>801.6182500000001</v>
+      </c>
+      <c r="K124" s="183">
+        <f t="shared" si="2"/>
+        <v>2207.5182500000001</v>
+      </c>
+      <c r="L124" s="215"/>
+      <c r="M124" s="216"/>
+      <c r="N124" s="216"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
+    <mergeCell ref="G114:N114"/>
+    <mergeCell ref="L115:N124"/>
+    <mergeCell ref="G111:N111"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="K113:L113"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="A1:E1"/>
@@ -6152,7 +6681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6252,7 +6781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6264,13 +6793,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="216" t="s">
+      <c r="A1" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218"/>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="223"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="122" t="s">
@@ -6412,7 +6941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -6819,7 +7348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -6828,13 +7357,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="142" t="s">
@@ -6934,13 +7463,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="219" t="s">
+      <c r="A8" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
+      <c r="B8" s="225"/>
+      <c r="C8" s="225"/>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="142" t="s">
@@ -7142,13 +7671,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="219" t="s">
+      <c r="A21" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="219"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="219"/>
+      <c r="B21" s="225"/>
+      <c r="C21" s="225"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="142" t="s">
@@ -7260,13 +7789,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="225" t="s">
+      <c r="A30" s="229" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="225"/>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
+      <c r="B30" s="229"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="150" t="s">
@@ -7303,13 +7832,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="222" t="s">
+      <c r="A33" s="226" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="223"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="224"/>
+      <c r="B33" s="227"/>
+      <c r="C33" s="227"/>
+      <c r="D33" s="227"/>
+      <c r="E33" s="228"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="150" t="s">
@@ -7404,13 +7933,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="220" t="s">
+      <c r="A42" s="224" t="s">
         <v>108</v>
       </c>
-      <c r="B42" s="220"/>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="162" t="s">
@@ -7544,13 +8073,13 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="220" t="s">
+      <c r="A51" s="224" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="220"/>
-      <c r="C51" s="220"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
+      <c r="B51" s="224"/>
+      <c r="C51" s="224"/>
+      <c r="D51" s="224"/>
+      <c r="E51" s="224"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="162" t="s">
@@ -7667,13 +8196,13 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="220" t="s">
+      <c r="A59" s="224" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="220"/>
-      <c r="C59" s="220"/>
-      <c r="D59" s="220"/>
-      <c r="E59" s="220"/>
+      <c r="B59" s="224"/>
+      <c r="C59" s="224"/>
+      <c r="D59" s="224"/>
+      <c r="E59" s="224"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="162" t="s">
@@ -7785,13 +8314,13 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="197" t="s">
+      <c r="A68" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="B68" s="197"/>
-      <c r="C68" s="197"/>
-      <c r="D68" s="197"/>
-      <c r="E68" s="197"/>
+      <c r="B68" s="202"/>
+      <c r="C68" s="202"/>
+      <c r="D68" s="202"/>
+      <c r="E68" s="202"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="123" t="s">
@@ -7828,13 +8357,13 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="221" t="s">
+      <c r="A73" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="221"/>
-      <c r="C73" s="221"/>
-      <c r="D73" s="221"/>
-      <c r="E73" s="221"/>
+      <c r="B73" s="230"/>
+      <c r="C73" s="230"/>
+      <c r="D73" s="230"/>
+      <c r="E73" s="230"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="156" t="s">
@@ -7917,13 +8446,13 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="221" t="s">
+      <c r="A79" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="221"/>
-      <c r="C79" s="221"/>
-      <c r="D79" s="221"/>
-      <c r="E79" s="221"/>
+      <c r="B79" s="230"/>
+      <c r="C79" s="230"/>
+      <c r="D79" s="230"/>
+      <c r="E79" s="230"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="156" t="s">
@@ -7972,13 +8501,13 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="219" t="s">
+      <c r="A85" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="219"/>
-      <c r="C85" s="219"/>
-      <c r="D85" s="219"/>
-      <c r="E85" s="219"/>
+      <c r="B85" s="225"/>
+      <c r="C85" s="225"/>
+      <c r="D85" s="225"/>
+      <c r="E85" s="225"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="142" t="s">
@@ -8015,13 +8544,13 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="219" t="s">
+      <c r="A88" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="219"/>
-      <c r="C88" s="219"/>
-      <c r="D88" s="219"/>
-      <c r="E88" s="219"/>
+      <c r="B88" s="225"/>
+      <c r="C88" s="225"/>
+      <c r="D88" s="225"/>
+      <c r="E88" s="225"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="142" t="s">
@@ -8087,13 +8616,13 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="219" t="s">
+      <c r="A93" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="219"/>
-      <c r="C93" s="219"/>
-      <c r="D93" s="219"/>
-      <c r="E93" s="219"/>
+      <c r="B93" s="225"/>
+      <c r="C93" s="225"/>
+      <c r="D93" s="225"/>
+      <c r="E93" s="225"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="142" t="s">
@@ -8172,12 +8701,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A93:E93"/>
@@ -8186,6 +8709,12 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8206,25 +8735,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="197" t="s">
+      <c r="A1" s="202" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="198" t="s">
+      <c r="A2" s="203" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="200"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="205"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9001,18 +9530,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="207" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -10189,39 +10718,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
     </row>
     <row r="2" spans="1:11" s="195" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="193" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="211" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="211"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
+      <c r="J2" s="212"/>
       <c r="K2" s="194" t="s">
         <v>6</v>
       </c>
@@ -10230,38 +10759,38 @@
       <c r="A3" s="193">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="211" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="213" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+      <c r="H3" s="213"/>
+      <c r="I3" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
-      <c r="K3" s="226">
+      <c r="J3" s="213"/>
+      <c r="K3" s="200">
         <f>C13+C19+G15+K16</f>
         <v>2125.2200000000003</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="208"/>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
+      <c r="A4" s="209"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
     </row>
     <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
@@ -10273,7 +10802,7 @@
       <c r="C5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="212"/>
+      <c r="D5" s="208"/>
       <c r="E5" s="175" t="s">
         <v>0</v>
       </c>
@@ -10283,7 +10812,7 @@
       <c r="G5" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="212"/>
+      <c r="H5" s="208"/>
       <c r="I5" s="175" t="s">
         <v>0</v>
       </c>
@@ -10304,7 +10833,7 @@
       <c r="C6" s="180">
         <v>114.46</v>
       </c>
-      <c r="D6" s="212"/>
+      <c r="D6" s="208"/>
       <c r="E6" s="178">
         <v>1</v>
       </c>
@@ -10314,7 +10843,7 @@
       <c r="G6" s="180">
         <v>73.849999999999994</v>
       </c>
-      <c r="H6" s="212"/>
+      <c r="H6" s="208"/>
       <c r="I6" s="178">
         <v>1</v>
       </c>
@@ -10335,7 +10864,7 @@
       <c r="C7" s="183">
         <v>69</v>
       </c>
-      <c r="D7" s="212"/>
+      <c r="D7" s="208"/>
       <c r="E7" s="181">
         <v>2</v>
       </c>
@@ -10345,7 +10874,7 @@
       <c r="G7" s="183">
         <v>72.41</v>
       </c>
-      <c r="H7" s="212"/>
+      <c r="H7" s="208"/>
       <c r="I7" s="181">
         <v>2</v>
       </c>
@@ -10366,7 +10895,7 @@
       <c r="C8" s="180">
         <v>69.06</v>
       </c>
-      <c r="D8" s="212"/>
+      <c r="D8" s="208"/>
       <c r="E8" s="178">
         <v>3</v>
       </c>
@@ -10376,7 +10905,7 @@
       <c r="G8" s="180">
         <v>68.52</v>
       </c>
-      <c r="H8" s="212"/>
+      <c r="H8" s="208"/>
       <c r="I8" s="178">
         <v>3</v>
       </c>
@@ -10397,7 +10926,7 @@
       <c r="C9" s="183">
         <v>69.319999999999993</v>
       </c>
-      <c r="D9" s="212"/>
+      <c r="D9" s="208"/>
       <c r="E9" s="181">
         <v>4</v>
       </c>
@@ -10407,7 +10936,7 @@
       <c r="G9" s="183">
         <v>68.55</v>
       </c>
-      <c r="H9" s="212"/>
+      <c r="H9" s="208"/>
       <c r="I9" s="181">
         <v>4</v>
       </c>
@@ -10428,7 +10957,7 @@
       <c r="C10" s="180">
         <v>69.03</v>
       </c>
-      <c r="D10" s="212"/>
+      <c r="D10" s="208"/>
       <c r="E10" s="178">
         <v>5</v>
       </c>
@@ -10438,7 +10967,7 @@
       <c r="G10" s="180">
         <v>68.64</v>
       </c>
-      <c r="H10" s="212"/>
+      <c r="H10" s="208"/>
       <c r="I10" s="178">
         <v>5</v>
       </c>
@@ -10459,7 +10988,7 @@
       <c r="C11" s="183">
         <v>68.28</v>
       </c>
-      <c r="D11" s="212"/>
+      <c r="D11" s="208"/>
       <c r="E11" s="181">
         <v>6</v>
       </c>
@@ -10469,7 +10998,7 @@
       <c r="G11" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H11" s="212"/>
+      <c r="H11" s="208"/>
       <c r="I11" s="181">
         <v>6</v>
       </c>
@@ -10490,7 +11019,7 @@
       <c r="C12" s="180">
         <v>137.83000000000001</v>
       </c>
-      <c r="D12" s="212"/>
+      <c r="D12" s="208"/>
       <c r="E12" s="178">
         <v>7</v>
       </c>
@@ -10500,7 +11029,7 @@
       <c r="G12" s="180">
         <v>67.58</v>
       </c>
-      <c r="H12" s="212"/>
+      <c r="H12" s="208"/>
       <c r="I12" s="178">
         <v>7</v>
       </c>
@@ -10520,7 +11049,7 @@
         <f>SUM(C6:C12)</f>
         <v>596.98</v>
       </c>
-      <c r="D13" s="212"/>
+      <c r="D13" s="208"/>
       <c r="E13" s="181">
         <v>8</v>
       </c>
@@ -10530,7 +11059,7 @@
       <c r="G13" s="183">
         <v>68.459999999999994</v>
       </c>
-      <c r="H13" s="212"/>
+      <c r="H13" s="208"/>
       <c r="I13" s="181">
         <v>8</v>
       </c>
@@ -10542,10 +11071,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="227"/>
-      <c r="B14" s="227"/>
-      <c r="C14" s="227"/>
-      <c r="D14" s="212"/>
+      <c r="A14" s="201"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="208"/>
       <c r="E14" s="178">
         <v>9</v>
       </c>
@@ -10555,7 +11084,7 @@
       <c r="G14" s="180">
         <v>68.27</v>
       </c>
-      <c r="H14" s="212"/>
+      <c r="H14" s="208"/>
       <c r="I14" s="178">
         <v>9</v>
       </c>
@@ -10576,7 +11105,7 @@
       <c r="C15" s="177" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="212"/>
+      <c r="D15" s="208"/>
       <c r="F15" s="182" t="s">
         <v>93</v>
       </c>
@@ -10584,7 +11113,7 @@
         <f>SUM(G6:G14)</f>
         <v>624.7399999999999</v>
       </c>
-      <c r="H15" s="212"/>
+      <c r="H15" s="208"/>
       <c r="I15" s="181">
         <v>10</v>
       </c>
@@ -10605,11 +11134,11 @@
       <c r="C16" s="180">
         <v>103.08</v>
       </c>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="208"/>
+      <c r="H16" s="208"/>
       <c r="J16" s="182" t="s">
         <v>93</v>
       </c>
@@ -10628,14 +11157,14 @@
       <c r="C17" s="183">
         <v>22.05</v>
       </c>
-      <c r="D17" s="212"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="212"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="212"/>
-      <c r="I17" s="212"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="212"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="208"/>
+      <c r="H17" s="208"/>
+      <c r="I17" s="208"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="178">
@@ -10647,14 +11176,14 @@
       <c r="C18" s="180">
         <v>30.97</v>
       </c>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="212"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="212"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="208"/>
+      <c r="F18" s="208"/>
+      <c r="G18" s="208"/>
+      <c r="H18" s="208"/>
+      <c r="I18" s="208"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="208"/>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="182"/>
@@ -10665,22 +11194,17 @@
         <f>SUM(C16:C18)</f>
         <v>156.1</v>
       </c>
-      <c r="D19" s="212"/>
-      <c r="E19" s="212"/>
-      <c r="F19" s="212"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="212"/>
-      <c r="I19" s="212"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="212"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="208"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="I17:K19"/>
-    <mergeCell ref="H5:H19"/>
-    <mergeCell ref="D5:D19"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="E16:G19"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -10688,6 +11212,11 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I17:K19"/>
+    <mergeCell ref="H5:H19"/>
+    <mergeCell ref="D5:D19"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="E16:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10696,222 +11225,250 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" customWidth="1"/>
-    <col min="6" max="6" width="25.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" customWidth="1"/>
     <col min="7" max="7" width="8.77734375" customWidth="1"/>
     <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-    </row>
-    <row r="2" spans="1:8" s="189" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="190" t="s">
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+    </row>
+    <row r="2" spans="1:8" s="199" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="190" t="s">
+      <c r="B2" s="234" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="235"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="237" t="s">
         <v>148</v>
       </c>
-      <c r="G2" s="191" t="s">
+      <c r="F2" s="238"/>
+      <c r="G2" s="197" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="173" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="190">
-        <v>1</v>
-      </c>
-      <c r="B3" s="207" t="s">
+    <row r="3" spans="1:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="196">
+        <v>1</v>
+      </c>
+      <c r="B3" s="234" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="196" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="192" t="s">
+      <c r="C3" s="235"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="239" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="240"/>
+      <c r="G3" s="198" t="s">
         <v>42</v>
       </c>
       <c r="H3" s="184">
-        <f>C12</f>
-        <v>1482.242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="203"/>
-      <c r="B4" s="203"/>
-      <c r="C4" s="203"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-    </row>
-    <row r="5" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+        <f>C14</f>
+        <v>1205.9000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="214"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+    </row>
+    <row r="5" spans="1:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="176" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="231" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="242"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="232">
+        <v>1</v>
+      </c>
+      <c r="B6" s="232" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="233">
+        <v>411.5</v>
+      </c>
+      <c r="D6" s="242"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
+      <c r="H6" s="241"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="232">
+        <v>2</v>
+      </c>
+      <c r="B7" s="232" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="233">
+        <v>128.1</v>
+      </c>
+      <c r="D7" s="242"/>
+      <c r="E7" s="241"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="232">
         <v>3</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="178" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="180">
-        <f>191.78+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
-        <v>262.21799999999996</v>
-      </c>
-      <c r="D6" s="204"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="181">
-        <v>2</v>
-      </c>
-      <c r="B7" s="181" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="183">
-        <f>146.45+59.6+0.942*13</f>
-        <v>218.29599999999999</v>
-      </c>
-      <c r="D7" s="204"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="181">
-        <v>3</v>
-      </c>
-      <c r="B8" s="181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="183">
-        <f>158.69+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
-        <v>229.12800000000001</v>
-      </c>
-      <c r="D8" s="204"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
+      <c r="B8" s="232" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="233">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="D8" s="242"/>
+      <c r="E8" s="241"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="181">
+      <c r="A9" s="232">
         <v>4</v>
       </c>
       <c r="B9" s="181" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="183">
-        <f>145.8+59.6+0.942*13</f>
-        <v>217.64600000000002</v>
-      </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
+        <v>32</v>
+      </c>
+      <c r="C9" s="233">
+        <v>53.400000000000006</v>
+      </c>
+      <c r="D9" s="242"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
     </row>
     <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="181">
+      <c r="A10" s="232">
         <v>5</v>
       </c>
       <c r="B10" s="181" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="183">
-        <f>243.62+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
-        <v>314.05799999999999</v>
-      </c>
-      <c r="D10" s="204"/>
-      <c r="E10" s="205"/>
-      <c r="F10" s="205"/>
-      <c r="G10" s="205"/>
-      <c r="H10" s="205"/>
+        <v>24</v>
+      </c>
+      <c r="C10" s="233">
+        <v>144.4</v>
+      </c>
+      <c r="D10" s="242"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="181">
+      <c r="A11" s="232">
         <v>6</v>
       </c>
-      <c r="B11" s="178" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="180">
-        <f>146.65+59.6+22.4+0.942*13</f>
-        <v>240.89600000000002</v>
-      </c>
-      <c r="D11" s="204"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="205"/>
-      <c r="H11" s="205"/>
+      <c r="B11" s="181" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="233">
+        <v>6.3999999999999986</v>
+      </c>
+      <c r="D11" s="242"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
     </row>
     <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="182"/>
-      <c r="B12" s="182" t="s">
+      <c r="A12" s="232">
+        <v>7</v>
+      </c>
+      <c r="B12" s="181" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="233">
+        <v>216.1</v>
+      </c>
+      <c r="D12" s="242"/>
+      <c r="E12" s="241"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="232">
+        <v>8</v>
+      </c>
+      <c r="B13" s="181" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="233">
+        <v>111.69999999999999</v>
+      </c>
+      <c r="D13" s="242"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="182"/>
+      <c r="B14" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="183">
-        <f>SUM(C6:C11)</f>
-        <v>1482.242</v>
-      </c>
-      <c r="D12" s="204"/>
-      <c r="E12" s="205"/>
-      <c r="F12" s="205"/>
-      <c r="G12" s="205"/>
-      <c r="H12" s="205"/>
+      <c r="C14" s="183">
+        <f t="shared" ref="C14" si="0">SUM(C6:C13)</f>
+        <v>1205.9000000000001</v>
+      </c>
+      <c r="D14" s="242"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="D5:H14"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="D5:H12"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -10920,165 +11477,223 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="6" width="8.77734375" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="1.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" customWidth="1"/>
-    <col min="10" max="10" width="2.88671875" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+    <row r="1" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-    </row>
-    <row r="2" spans="1:11" s="188" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="187" t="s">
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+    </row>
+    <row r="2" spans="1:8" s="189" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="190" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="207" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="B2" s="234" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="235"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="237" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="209" t="s">
+      <c r="F2" s="238"/>
+      <c r="G2" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="173" t="s">
+      <c r="H2" s="173" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="187">
-        <v>1</v>
-      </c>
-      <c r="B3" s="207" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="210" t="s">
-        <v>185</v>
-      </c>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210" t="s">
+    <row r="3" spans="1:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="190">
+        <v>1</v>
+      </c>
+      <c r="B3" s="234" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="235"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="239" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3" s="240"/>
+      <c r="G3" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="210"/>
-      <c r="K3" s="184">
-        <f>C7</f>
-        <v>167.53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="208"/>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="184">
+        <f>C12</f>
+        <v>1482.242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="214"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+    </row>
+    <row r="5" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="175" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="176" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="231" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="215"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="178">
+        <v>1</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="180">
+        <f t="shared" ref="C6" si="0">191.78+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>262.21799999999996</v>
+      </c>
+      <c r="D6" s="215"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="183">
+        <f t="shared" ref="C7" si="1">146.45+59.6+0.942*13</f>
+        <v>218.29599999999999</v>
+      </c>
+      <c r="D7" s="215"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
         <v>3</v>
       </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="178">
-        <v>1</v>
-      </c>
-      <c r="B6" s="179" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="180">
-        <v>167.53</v>
-      </c>
-      <c r="D6" s="204"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="182" t="s">
+      <c r="B8" s="181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="183">
+        <f t="shared" ref="C8" si="2">158.69+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>229.12800000000001</v>
+      </c>
+      <c r="D8" s="215"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="183">
+        <f t="shared" ref="C9" si="3">145.8+59.6+0.942*13</f>
+        <v>217.64600000000002</v>
+      </c>
+      <c r="D9" s="215"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
+        <v>5</v>
+      </c>
+      <c r="B10" s="181" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="183">
+        <f t="shared" ref="C10" si="4">243.62+15.6*3+0.4*0.4*6.2+13*0.1*2*4+0.942*13</f>
+        <v>314.05799999999999</v>
+      </c>
+      <c r="D10" s="215"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="216"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
+        <v>6</v>
+      </c>
+      <c r="B11" s="178" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="180">
+        <f t="shared" ref="C11" si="5">146.65+59.6+22.4+0.942*13</f>
+        <v>240.89600000000002</v>
+      </c>
+      <c r="D11" s="215"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="182"/>
+      <c r="B12" s="182" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="182" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="183">
-        <f>SUM(C6:C6)</f>
-        <v>167.53</v>
-      </c>
-      <c r="D7" s="204"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
+      <c r="C12" s="183">
+        <f t="shared" ref="C12" si="6">SUM(C6:C11)</f>
+        <v>1482.242</v>
+      </c>
+      <c r="D12" s="215"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="216"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="D5:K7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
+  <mergeCells count="7">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="D5:H12"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
